--- a/data/trans_orig/P36BPD01_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD01_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si utilizan como principal grasa para cocinar el aceite de oliva en 2023</t>
+          <t>Población según si utilizan como principal grasa para cocinar el aceite de oliva en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>284552</t>
+          <t>284602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>300183</t>
+          <t>301254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>255976</t>
+          <t>255738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>271250</t>
+          <t>271495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>545817</t>
+          <t>546478</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>568310</t>
+          <t>568508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26891</t>
+          <t>26841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33659</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32767</t>
+          <t>32569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55260</t>
+          <t>54599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>398391</t>
+          <t>404489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>449808</t>
+          <t>451312</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,82 +1088,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>88,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>445534</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>431327</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>457734</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>87,12%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>84,34%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>875691</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>846698</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>901583</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>82,97%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>88,35%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>445534</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>430657</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>456719</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>87,12%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>84,21%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>875691</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>845460</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>901338</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>85,81%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>82,85%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59290</t>
+          <t>57786</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110707</t>
+          <t>104609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,82 +1201,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>65862</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>53662</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>80069</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>144803</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>118911</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>173796</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>11,65%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>65862</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>54677</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>80739</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,88%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>144803</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>119156</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>175034</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>309769</t>
+          <t>310647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>339248</t>
+          <t>340086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>346608</t>
+          <t>346627</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>651873</t>
+          <t>652366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>660032</t>
+          <t>659963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>301380</t>
+          <t>301169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>310444</t>
+          <t>310209</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>453652</t>
+          <t>451738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>472571</t>
+          <t>472351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>759925</t>
+          <t>759374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>781010</t>
+          <t>780949</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28349</t>
+          <t>28900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>164224</t>
+          <t>163497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174492</t>
+          <t>174572</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196159</t>
+          <t>195328</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204720</t>
+          <t>204474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>364640</t>
+          <t>364372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>377673</t>
+          <t>377656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>15245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12946</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>22644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>264351</t>
+          <t>264451</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>269302</t>
+          <t>269306</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>246188</t>
+          <t>245346</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>255104</t>
+          <t>254927</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>512848</t>
+          <t>513211</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>523388</t>
+          <t>523200</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>590129</t>
+          <t>589914</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>607525</t>
+          <t>607253</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>818861</t>
+          <t>819068</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>841051</t>
+          <t>841323</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1415023</t>
+          <t>1415077</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1444861</t>
+          <t>1444677</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27291</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30404</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21823</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51661</t>
+          <t>51607</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>874099</t>
+          <t>872622</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>915142</t>
+          <t>913217</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>676192</t>
+          <t>675747</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>694857</t>
+          <t>695346</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1560770</t>
+          <t>1560854</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1606324</t>
+          <t>1605567</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13578</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54621</t>
+          <t>56098</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39913</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38502</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>84056</t>
+          <t>83972</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3242677</t>
+          <t>3239663</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3318017</t>
+          <t>3314832</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3468372</t>
+          <t>3467078</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3524900</t>
+          <t>3528030</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6728011</t>
+          <t>6725947</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6820115</t>
+          <t>6823898</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>123690</t>
+          <t>126875</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>199030</t>
+          <t>202044</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>130519</t>
+          <t>127389</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>187047</t>
+          <t>188341</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>277011</t>
+          <t>273228</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>369115</t>
+          <t>371179</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD01_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD01_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>293890</t>
+          <t>292561</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>284602</t>
+          <t>282266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>301254</t>
+          <t>301257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>265155</t>
+          <t>282302</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>255738</t>
+          <t>270634</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>271495</t>
+          <t>290231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>559044</t>
+          <t>574863</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>546478</t>
+          <t>560571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>568508</t>
+          <t>587267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>26284</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>17588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26841</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>33759</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>25830</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>45427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>42033</t>
+          <t>60043</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32569</t>
+          <t>47639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54599</t>
+          <t>74335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>430157</t>
+          <t>444827</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>404489</t>
+          <t>421469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>451312</t>
+          <t>464845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>445534</t>
+          <t>472363</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>431327</t>
+          <t>456994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>457734</t>
+          <t>484318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>875691</t>
+          <t>917190</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>846698</t>
+          <t>883905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>901583</t>
+          <t>939754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>78941</t>
+          <t>76725</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57786</t>
+          <t>56707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104609</t>
+          <t>100083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>65862</t>
+          <t>69434</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53662</t>
+          <t>57479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80069</t>
+          <t>84803</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>144803</t>
+          <t>146159</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118911</t>
+          <t>123595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173796</t>
+          <t>179444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>509098</t>
+          <t>521552</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>509098</t>
+          <t>521552</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>509098</t>
+          <t>521552</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511396</t>
+          <t>541797</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511396</t>
+          <t>541797</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511396</t>
+          <t>541797</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1020494</t>
+          <t>1063349</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1020494</t>
+          <t>1063349</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1020494</t>
+          <t>1063349</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>313052</t>
+          <t>311355</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>310647</t>
+          <t>306086</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>313927</t>
+          <t>313476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>344289</t>
+          <t>349358</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>340086</t>
+          <t>342378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>346627</t>
+          <t>352823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>657342</t>
+          <t>660713</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>652366</t>
+          <t>653147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>659963</t>
+          <t>665104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314091</t>
+          <t>314158</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314091</t>
+          <t>314158</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314091</t>
+          <t>314158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347971</t>
+          <t>355312</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347971</t>
+          <t>355312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347971</t>
+          <t>355312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>662062</t>
+          <t>669470</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>662062</t>
+          <t>669470</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>662062</t>
+          <t>669470</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>307337</t>
+          <t>363951</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>301169</t>
+          <t>353814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>310209</t>
+          <t>369153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>466938</t>
+          <t>412146</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>451738</t>
+          <t>398234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>472351</t>
+          <t>417687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>774273</t>
+          <t>776098</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>759374</t>
+          <t>759907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>780949</t>
+          <t>783891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>19331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14001</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28900</t>
+          <t>35200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>171234</t>
+          <t>192485</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>163497</t>
+          <t>185226</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174572</t>
+          <t>198225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>201615</t>
+          <t>219228</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>195328</t>
+          <t>215200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204474</t>
+          <t>222271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>372849</t>
+          <t>411713</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>364372</t>
+          <t>401683</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>377656</t>
+          <t>417662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>20439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>14167</t>
+          <t>20775</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22644</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>267930</t>
+          <t>267689</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>264451</t>
+          <t>263088</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>269306</t>
+          <t>269825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>251825</t>
+          <t>257588</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>245346</t>
+          <t>250882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>254927</t>
+          <t>260844</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>519755</t>
+          <t>525277</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>513211</t>
+          <t>518040</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>523200</t>
+          <t>529328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>600355</t>
+          <t>686726</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>589914</t>
+          <t>671860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>607253</t>
+          <t>697149</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>831035</t>
+          <t>744160</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>819068</t>
+          <t>731658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>841323</t>
+          <t>753097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1431389</t>
+          <t>1430885</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1415077</t>
+          <t>1413791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1444677</t>
+          <t>1446376</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27506</t>
+          <t>41484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>27897</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>18960</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>40399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>35295</t>
+          <t>54516</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51607</t>
+          <t>71610</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>617420</t>
+          <t>713344</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>617420</t>
+          <t>713344</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>617420</t>
+          <t>713344</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1466684</t>
+          <t>1485401</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1466684</t>
+          <t>1485401</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1466684</t>
+          <t>1485401</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>892491</t>
+          <t>739023</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>872622</t>
+          <t>719430</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>913217</t>
+          <t>752366</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>687362</t>
+          <t>787035</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>675747</t>
+          <t>772845</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>695346</t>
+          <t>798441</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1579854</t>
+          <t>1526058</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1560854</t>
+          <t>1501979</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1605567</t>
+          <t>1545401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>59049</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>45706</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56098</t>
+          <t>78642</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>42555</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20759</t>
+          <t>31149</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40358</t>
+          <t>56745</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>64972</t>
+          <t>101604</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39259</t>
+          <t>82261</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>83972</t>
+          <t>125683</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716105</t>
+          <t>829590</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716105</t>
+          <t>829590</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716105</t>
+          <t>829590</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644826</t>
+          <t>1627662</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644826</t>
+          <t>1627662</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644826</t>
+          <t>1627662</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3276446</t>
+          <t>3298616</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3239663</t>
+          <t>3260980</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3314832</t>
+          <t>3328952</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3493752</t>
+          <t>3524181</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3467078</t>
+          <t>3495998</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3528030</t>
+          <t>3551130</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6770198</t>
+          <t>6822797</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6725947</t>
+          <t>6771769</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6823898</t>
+          <t>6861831</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>165261</t>
+          <t>216872</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>126875</t>
+          <t>186536</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>202044</t>
+          <t>254508</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>161667</t>
+          <t>203171</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>127389</t>
+          <t>176222</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>188341</t>
+          <t>231354</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>326928</t>
+          <t>420043</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>273228</t>
+          <t>381009</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>371179</t>
+          <t>471071</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3441707</t>
+          <t>3515488</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3441707</t>
+          <t>3515488</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3441707</t>
+          <t>3515488</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3655419</t>
+          <t>3727352</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3655419</t>
+          <t>3727352</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3655419</t>
+          <t>3727352</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7097126</t>
+          <t>7242840</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7097126</t>
+          <t>7242840</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7097126</t>
+          <t>7242840</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
